--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="账号" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>题库类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -447,6 +452,11 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>示例管理员账号</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>S</t>
         </is>
       </c>
     </row>
